--- a/education_surveys/022_faculty_remote_work_productivity_survey--education_surveys.xlsx
+++ b/education_surveys/022_faculty_remote_work_productivity_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1723,8 +1723,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'very_satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'somewhat_satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_dissatisfied'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'somewhat_dissatisfied'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'very_dissatisfied'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'very_dissatisfied'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'neither_satisfied_nor_dissatisfied'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
